--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II - BI and AI Analytics for Data platform</t>
+          <t>Innovation Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Stantec</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, MySQL, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a66cd2257457c1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d8b5ed871430ded</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - BI and AI Analytics for Data platform</t>
+          <t>Software Engineer III - Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, BigQuery, Redshift, MySQL, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b82f810f63214a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Hybrid (San Francisco or Austin)</t>
+          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zendesk</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Snowflake, Power BI, Python, R</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190a827f8e23b77</t>
+          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer Test Automation</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Titusville, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,104 +591,104 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d815923c503c41e</t>
+          <t>https://www.indeed.com/viewjob?jk=a25095c67cb7b1fa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Growth Marketing Engineer, Worker Experience</t>
+          <t>Gen AI - Senior Software Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Workwhile</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, PostgreSQL, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Jenkins, Hadoop, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc09aac831ecc5c</t>
+          <t>https://www.indeed.com/viewjob?jk=e39b91b2ae393c3a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Developer - Platform Engineering</t>
+          <t>Gen AI - Senior Software Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Redfin</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Jenkins, Hadoop, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e87cd9454b0f743</t>
+          <t>https://www.indeed.com/viewjob?jk=deab1c187227eda3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Independent Contractor (1099) – Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Phoenix Rescue Mission</t>
+          <t>Applied Systems</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,192 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcb43cd5ba3fa371</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Applied AI ML, Senior Associate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc7bacc26a56bf13</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=086d2fe0c185a40f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Agents and Generative AI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Vantor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b55790d9a7d3967</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Agents and Generative AI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Vantor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bbe13645f41b7940</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vantor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caae1ea59627b7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer, AI Agents &amp; Generative AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Vantor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ec59c5175b9e68</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Innovation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stantec</t>
+          <t>InterImage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Databricks, Python</t>
+          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, S3, EC2, Kinesis, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d8b5ed871430ded</t>
+          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack Engineer</t>
+          <t>Ld Software Engineer, AI &amp; Data Applications</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, SQL</t>
+          <t>RAG, Gemini, Glue, BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9bac7d17ad25cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f645efaf8937a78a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Project Delivery Senior Analyst - API &amp; Azure DevOps Developer - Remote</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ISHIR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1949efd776a6da0e</t>
+          <t>https://www.indeed.com/viewjob?jk=aba78f30caeb6b9c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer Test Automation</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Titusville, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a25095c67cb7b1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5b38e17aa2f2e316</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gen AI - Senior Software Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Jenkins, Hadoop, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39b91b2ae393c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac338f6744153fa1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI - Senior Software Automation Engineer</t>
+          <t>FinOps engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Xsolla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Jenkins, Hadoop, Python, R, Java</t>
+          <t>RAG, BigQuery, Kubernetes, Terraform, Git, BigQuery, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deab1c187227eda3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f59b1c8503d9aef</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>QA Automation Engineer Intern</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Applied Systems</t>
+          <t>Canon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb43cd5ba3fa371</t>
+          <t>https://www.indeed.com/viewjob?jk=ee036fb551737016</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Applied AI ML, Senior Associate</t>
+          <t>Intern - Computer Engineer, AI/ML/LLM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,157 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Python, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, ChromaDB, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086d2fe0c185a40f</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents and Generative AI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b55790d9a7d3967</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents and Generative AI</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bbe13645f41b7940</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Westminster, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=caae1ea59627b7b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer, AI Agents &amp; Generative AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Vantor</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Gemini, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ec59c5175b9e68</t>
+          <t>https://www.indeed.com/viewjob?jk=20dda6adbad060a5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Junior Integration Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>InterImage</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Guaynabo, PR, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, TensorFlow, PyTorch, S3, EC2, Kinesis, Docker, Kubernetes</t>
+          <t>RAG, BigQuery, Docker, Git, BigQuery, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b5cd9ecf25f6cbb</t>
+          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ld Software Engineer, AI &amp; Data Applications</t>
+          <t>Specialist, Data Engineer (Hybrid - Rahway, NJ)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Glue, BigQuery, CI/CD, Git, BigQuery, Tableau, Python, SQL</t>
+          <t>RAG, Prompt Engineering, Redshift, Git, Redshift, Power BI, Python, R, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,217 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f645efaf8937a78a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ISHIR</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aba78f30caeb6b9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Generative AI Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Vforce Infotech</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Edison, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b38e17aa2f2e316</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Disney Experiences</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac338f6744153fa1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FinOps engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Xsolla</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Kubernetes, Terraform, Git, BigQuery, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f59b1c8503d9aef</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Canon</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee036fb551737016</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Intern - Computer Engineer, AI/ML/LLM</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, ChromaDB, TensorFlow, PyTorch, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20dda6adbad060a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4770245cd0fab45f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,560 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Junior Integration Developer</t>
+          <t>AWS SageMaker Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Guaynabo, PR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Git, BigQuery, Power BI, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, AWS SageMaker, S3, Glue, Athena, Redshift, MLflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e14330f4b7345b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer (Hybrid - Rahway, NJ)</t>
+          <t>AWS Python Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>RecruitIQ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Data Lake, Kafka, Hadoop, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Devengine</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Python, R</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=784f3aac2bb76b95</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Data Architect - Databricks</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, CI/CD, Git, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Python/ Gen AI/ AWS Engineer.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S Mobile Wireless LLC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Moline, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, FastAPI, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e38b188e4fcf5150</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Scientist II (Healthcare)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Cambia Health Solutions</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b01fe6ae2478bc92</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Scientist I (Healthcare)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cambia Health Solutions</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Renton, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec6898011e0225ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Azure Databricks and Oracle Tester</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sr Quality Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9a342f8fe663907</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Engineer, SRE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sephora</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a224ecf9f0a3ffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer, Martech New</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The Knot Worldwide</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdb5a7b856c54d9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Redshift, Git, Redshift, Power BI, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4770245cd0fab45f</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0db6800eee6c113</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ontic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f1b63814a7dff66</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Genentech</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86d58bc1aadabfce</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c8bb8abf6b6812a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS SageMaker Data Scientist</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, AWS SageMaker, S3, Glue, Athena, Redshift, MLflow</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d132dfef0009f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=4db823946a6a7e7a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Python Developer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RecruitIQ</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Data Lake, Kafka, Hadoop, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb62ed22823ef00</t>
+          <t>https://www.indeed.com/viewjob?jk=0e0dbbab007106f2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Devengine</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=784f3aac2bb76b95</t>
+          <t>https://www.indeed.com/viewjob?jk=021e404c023c8849</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect - Databricks</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, CI/CD, Git, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ac4e591f657264f</t>
+          <t>https://www.indeed.com/viewjob?jk=46cb9563b8b5288a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python/ Gen AI/ AWS Engineer.</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S Mobile Wireless LLC</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Moline, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, S3, EC2, FastAPI, CI/CD, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38b188e4fcf5150</t>
+          <t>https://www.indeed.com/viewjob?jk=9360c914c91500bf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Scientist II (Healthcare)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01fe6ae2478bc92</t>
+          <t>https://www.indeed.com/viewjob?jk=38afd377d6959ec2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Scientist I (Healthcare)</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cambia Health Solutions</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>25.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec6898011e0225ec</t>
+          <t>https://www.indeed.com/viewjob?jk=495df21035c6c9f7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>25.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cebf8689f1477182</t>
+          <t>https://www.indeed.com/viewjob?jk=3b407e8e73833abb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Quality Engineer - Remote</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>25.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, Git, Snowflake, Databricks, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a342f8fe663907</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed8d499b33fd43e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, SRE</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>25.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a224ecf9f0a3ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb93827e4757857</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Martech New</t>
+          <t>Python Developer with AWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>Data Scientist, S3, EC2, Glue, Redshift, Docker, Kubernetes, CI/CD, Git, Redshift</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c82af06849de41ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Analyst</t>
+          <t>Sr. Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lowell, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdb5a7b856c54d9d</t>
+          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0db6800eee6c113</t>
+          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DEVELOPER L3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ontic</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>East Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1b63814a7dff66</t>
+          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,287 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d58bc1aadabfce</t>
+          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>GenAI Engineer- Python</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Azure ML, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dad64d473e85eb76</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gen AI Engineer_Python</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Infosys</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Azure ML, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6d9935d29fcf39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cffd2e29a1e3837</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Software Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62fe5ebae46e1471</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer - Digital Experiences &amp; Capabilities</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8bb8abf6b6812a</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, Tableau, Power BI, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37d7123f90f360af</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ONTIC TECHNOLOGIES</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ded9320e66fcc57</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Allen Park, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Terraform, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97c354385113fcea</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Symhas</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Hadoop, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Python Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4db823946a6a7e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tosh, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>Data Scientist, RAG, S3, Redshift, Git, Redshift, Hadoop, MySQL, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e0dbbab007106f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2048f86dc25d51f2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021e404c023c8849</t>
+          <t>https://www.indeed.com/viewjob?jk=22595af7a8f7c897</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>V2X</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Harvard, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cb9563b8b5288a</t>
+          <t>https://www.indeed.com/viewjob?jk=107cc51a4be6da4d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>VaxCare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9360c914c91500bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b7612e10491ad26f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Azure Databricks and Oracle Tester</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38afd377d6959ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Customer Support Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=495df21035c6c9f7</t>
+          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b407e8e73833abb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineering Intern Atlanta, GA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Greenlight Financial Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.6</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>RAG, S3, EC2, Apache Airflow, Terraform, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed8d499b33fd43e</t>
+          <t>https://www.indeed.com/viewjob?jk=41f699edbfeee446</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.6</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, FastAPI, CI/CD</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Power BI, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb93827e4757857</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Python Developer with AWS</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, Redshift, Docker, Kubernetes, CI/CD, Git, Redshift</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa709d11e93dc2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=29c590e4580810e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Backend</t>
+          <t>Sr. Marketing Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>Generative AI, LangChain, LLaMA, XGBoost, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,392 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80f0b473fc9d61ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b0895dce8e54cd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DEVELOPER L3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Wipro</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>East Brunswick, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Databricks</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=572120ce80028ef5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Gallagher</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rolling Meadows, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88f6d60e8f8c8637</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GenAI Engineer- Python</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Infosys</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Azure ML, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop, Python</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dad64d473e85eb76</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Gen AI Engineer_Python</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Infosys</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Azure ML, BigQuery, CI/CD, Snowflake, BigQuery, Hadoop, Python</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6d9935d29fcf39</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior, Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Sam's Club</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cffd2e29a1e3837</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>(USA) Senior, Software Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Sam's Club</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62fe5ebae46e1471</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Engineer - Digital Experiences &amp; Capabilities</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Git, Hadoop, Tableau, Power BI, R, Scala, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37d7123f90f360af</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ONTIC TECHNOLOGIES</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ded9320e66fcc57</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Allen Park, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Terraform, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97c354385113fcea</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Symhas</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pleasanton, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Hadoop, Python, SQL, R, Scala, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be223724b244509d</t>
+          <t>https://www.indeed.com/viewjob?jk=aaacdaec37062c05</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-02.xlsx
+++ b/daily_matches/job_matches_2026-04-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Data Engineer/Data Scientist</t>
+          <t>Data Science Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Premise Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Redshift, BigQuery, CI/CD, Snowflake, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9f9bba74d522f56</t>
+          <t>https://www.indeed.com/viewjob?jk=2f86ec27477ecc7b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Mid-Junior DevOps Engineer - USA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tosh, Inc.</t>
+          <t>HERE Technologies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Git, Redshift, Hadoop, MySQL, Tableau, Power BI</t>
+          <t>EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048f86dc25d51f2</t>
+          <t>https://www.indeed.com/viewjob?jk=f3e439f3587c870f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Intapp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, NoSQL, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22595af7a8f7c897</t>
+          <t>https://www.indeed.com/viewjob?jk=64cabc38ac6fdf05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V2X</t>
+          <t>Headspace</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Harvard, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>RAG, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift, PySpark, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=107cc51a4be6da4d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd766141c2ef3c09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI / ML Solution Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VaxCare</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Jenkins, GitHub Actions, Git, Databricks, PySpark, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, TensorFlow, PyTorch, Glue, Docker, CI/CD, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7612e10491ad26f</t>
+          <t>https://www.indeed.com/viewjob?jk=beb104dd58edc16a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Databricks and Oracle Tester</t>
+          <t>AI Cloud Engineer (contract)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hilton</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,46 +657,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Jenkins, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, AWS SageMaker, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69623f6f14f8d6ba</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a841d23ada6319</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Customer Support Developer</t>
+          <t>Senior Software Engineer, Full Stack</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Airbyte</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f9bcd1ed45f0f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9da9f4175d28bd4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Snowflake</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CI/CD, Databricks, Kafka, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Apache Airflow, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b976f19ca042be6</t>
+          <t>https://www.indeed.com/viewjob?jk=f93df4671eb35854</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineering Intern Atlanta, GA</t>
+          <t>Production Support Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Greenlight Financial Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Apache Airflow, Terraform, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Git, Snowflake, Databricks, PySpark, Kafka, Tableau, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f699edbfeee446</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b54dba08b36515</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Power BI, R, Scala</t>
+          <t>RAG, Glue, CI/CD, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd1d6f0d7bc11e8</t>
+          <t>https://www.indeed.com/viewjob?jk=10c2989515c7a228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer</t>
+          <t>Sr Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LendingClub</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R</t>
+          <t>Generative AI, RAG, Copilot, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,147 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c590e4580810e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab5a5ee3fa7f76</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Marketing Analytics Engineer</t>
+          <t>Data Scientist, NA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcbe23f3d87c318f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a1cec25876be4d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, LLaMA, XGBoost, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aaacdaec37062c05</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2348b23e6ebaa75c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5da2c94e9bdc6f05</t>
         </is>
       </c>
     </row>
